--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551020.9178398091</v>
+        <v>551021</v>
       </c>
       <c r="R5" t="n">
-        <v>6896497.430017011</v>
+        <v>6896498</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1096,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,11 +1040,6 @@
       </c>
       <c r="E5" t="n">
         <v>219790</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,6 +1040,11 @@
       </c>
       <c r="E5" t="n">
         <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20628-2022 artfynd.xlsx
+++ b/artfynd/A 20628-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>99444283</v>
       </c>
       <c r="B5" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
